--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6665-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6665-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19AB8018-EE87-451B-8F46-09D045E24F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{907E0647-40F3-4282-BCC9-3B1657F9CC65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{3349AF99-1B3C-4C23-9E10-39C91A1F3147}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{12772896-A60B-4ED8-B19C-DB0DCCFA5B9A}"/>
   </bookViews>
   <sheets>
     <sheet name="6665-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1457,30 +1457,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{983ED2FD-CC66-4BD4-9257-90F26BA34251}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB2F757C-E020-4AFC-B982-9D1682D1DC5E}">
   <dimension ref="A1:X15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="8.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="8.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="7" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="7" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1514,7 +1514,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1550,7 +1550,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1670,7 +1670,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>2.2200000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>33</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>33</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2019</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2018</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2017</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
         <v>41</v>
       </c>
